--- a/generador/plantillas/AL/C02-0001.xlsx
+++ b/generador/plantillas/AL/C02-0001.xlsx
@@ -2526,15 +2526,31 @@
           <t>Lecto-escritura (C03) cuando aplique</t>
         </is>
       </c>
-      <c r="B53" s="159" t="n"/>
+      <c r="B53" s="159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{EDU_LECTO_INSTITUCION}}</t>
+        </is>
+      </c>
       <c r="C53" s="102" t="n"/>
       <c r="D53" s="102" t="n"/>
       <c r="E53" s="102" t="n"/>
       <c r="F53" s="102" t="n"/>
       <c r="G53" s="101" t="n"/>
-      <c r="H53" s="159" t="n"/>
-      <c r="I53" s="159" t="n"/>
-      <c r="J53" s="159" t="n"/>
+      <c r="H53" s="159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{EDU_LECTO_PAIS}}</t>
+        </is>
+      </c>
+      <c r="I53" s="159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{EDU_LECTO_CIUDAD}}</t>
+        </is>
+      </c>
+      <c r="J53" s="159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{EDU_LECTO_TITULO}}</t>
+        </is>
+      </c>
       <c r="K53" s="102" t="n"/>
       <c r="L53" s="102" t="n"/>
       <c r="M53" s="101" t="n"/>
